--- a/Config/Datas/Tables/b_表现集合_VisualSetConfig.xlsx
+++ b/Config/Datas/Tables/b_表现集合_VisualSetConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbVisualSet" sheetId="1" r:id="R8610a334e0ad4730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbVisualSet" sheetId="1" r:id="R30de889fb6404c28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +103,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF64748B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -180,7 +200,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,6 +310,27 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -500,6 +541,7 @@
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -524,6 +566,9 @@
       <x:c r="G1" s="11" t="str">
         <x:v>scalePermille</x:v>
       </x:c>
+      <x:c r="H1" s="43" t="str">
+        <x:v>attackClipId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -546,6 +591,9 @@
       </x:c>
       <x:c r="G2" s="14" t="str">
         <x:v>int</x:v>
+      </x:c>
+      <x:c r="H2" s="44" t="str">
+        <x:v>int?#ref=TbAnimationClip</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -558,6 +606,7 @@
       <x:c r="E3" s="16"/>
       <x:c r="F3" s="16"/>
       <x:c r="G3" s="16"/>
+      <x:c r="H3" s="41"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="31" t="str">
@@ -570,7 +619,7 @@
         <x:v>表现类别</x:v>
       </x:c>
       <x:c r="D4" s="23" t="str">
-        <x:v>已确认的站立片段；可空</x:v>
+        <x:v>主角 fd、怪物 zd；缺少则留空</x:v>
       </x:c>
       <x:c r="E4" s="23" t="str">
         <x:v>已确认的移动片段；可空</x:v>
@@ -580,6 +629,9 @@
       </x:c>
       <x:c r="G4" s="24" t="str">
         <x:v>表现缩放，1000=原始大小</x:v>
+      </x:c>
+      <x:c r="H4" s="41" t="str">
+        <x:v>已核验怪物普攻 gj；其余留空</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -602,6 +654,7 @@
       <x:c r="G5" s="35" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H5" s="41"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
@@ -623,6 +676,7 @@
       <x:c r="G6" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H6" s="41"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33"/>
@@ -644,6 +698,7 @@
       <x:c r="G7" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H7" s="41"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33"/>
@@ -665,6 +720,7 @@
       <x:c r="G8" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H8" s="41"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33"/>
@@ -686,6 +742,7 @@
       <x:c r="G9" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H9" s="41"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33"/>
@@ -703,6 +760,7 @@
       <x:c r="G10" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H10" s="41"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33"/>
@@ -724,6 +782,7 @@
       <x:c r="G11" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H11" s="41"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33"/>
@@ -745,6 +804,7 @@
       <x:c r="G12" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H12" s="41"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33"/>
@@ -766,6 +826,7 @@
       <x:c r="G13" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H13" s="41"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33"/>
@@ -787,6 +848,7 @@
       <x:c r="G14" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H14" s="41"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33"/>
@@ -808,6 +870,7 @@
       <x:c r="G15" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H15" s="41"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33"/>
@@ -829,6 +892,7 @@
       <x:c r="G16" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H16" s="41"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33"/>
@@ -850,6 +914,7 @@
       <x:c r="G17" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H17" s="41"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33"/>
@@ -871,6 +936,7 @@
       <x:c r="G18" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H18" s="41"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33"/>
@@ -892,6 +958,7 @@
       <x:c r="G19" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H19" s="41"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="33"/>
@@ -913,6 +980,7 @@
       <x:c r="G20" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H20" s="41"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33"/>
@@ -934,6 +1002,7 @@
       <x:c r="G21" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H21" s="41"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="33"/>
@@ -955,6 +1024,7 @@
       <x:c r="G22" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H22" s="41"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="33"/>
@@ -976,6 +1046,7 @@
       <x:c r="G23" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H23" s="41"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="33"/>
@@ -997,6 +1068,7 @@
       <x:c r="G24" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H24" s="41"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="33"/>
@@ -1018,6 +1090,7 @@
       <x:c r="G25" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H25" s="41"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="33"/>
@@ -1039,6 +1112,7 @@
       <x:c r="G26" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H26" s="41"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="33"/>
@@ -1060,6 +1134,7 @@
       <x:c r="G27" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H27" s="41"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="33"/>
@@ -1081,6 +1156,7 @@
       <x:c r="G28" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H28" s="41"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="33"/>
@@ -1102,6 +1178,7 @@
       <x:c r="G29" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H29" s="41"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="33"/>
@@ -1123,6 +1200,7 @@
       <x:c r="G30" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H30" s="41"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="33"/>
@@ -1144,6 +1222,7 @@
       <x:c r="G31" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H31" s="41"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="33"/>
@@ -1165,6 +1244,7 @@
       <x:c r="G32" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H32" s="41"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="33"/>
@@ -1186,6 +1266,7 @@
       <x:c r="G33" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H33" s="41"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="33"/>
@@ -1207,6 +1288,7 @@
       <x:c r="G34" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H34" s="41"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="33"/>
@@ -1228,6 +1310,7 @@
       <x:c r="G35" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H35" s="41"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="33"/>
@@ -1245,6 +1328,7 @@
       <x:c r="G36" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H36" s="41"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="33"/>
@@ -1262,6 +1346,7 @@
       <x:c r="G37" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H37" s="41"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="33"/>
@@ -1279,6 +1364,7 @@
       <x:c r="G38" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H38" s="41"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="33"/>
@@ -1296,6 +1382,7 @@
       <x:c r="G39" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H39" s="41"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="33"/>
@@ -1313,6 +1400,7 @@
       <x:c r="G40" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H40" s="41"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="33"/>
@@ -1330,6 +1418,7 @@
       <x:c r="G41" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H41" s="41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="33"/>
@@ -1347,6 +1436,7 @@
       <x:c r="G42" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H42" s="41"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="33"/>
@@ -1364,6 +1454,7 @@
       <x:c r="G43" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H43" s="41"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="33"/>
@@ -1381,6 +1472,7 @@
       <x:c r="G44" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H44" s="41"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="33"/>
@@ -1398,6 +1490,7 @@
       <x:c r="G45" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H45" s="41"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="33"/>
@@ -1415,6 +1508,7 @@
       <x:c r="G46" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H46" s="41"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="33"/>
@@ -1432,6 +1526,7 @@
       <x:c r="G47" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H47" s="41"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="33"/>
@@ -1449,6 +1544,7 @@
       <x:c r="G48" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H48" s="41"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="33"/>
@@ -1466,6 +1562,7 @@
       <x:c r="G49" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H49" s="41"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="33"/>
@@ -1483,6 +1580,7 @@
       <x:c r="G50" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H50" s="41"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="33"/>
@@ -1500,6 +1598,7 @@
       <x:c r="G51" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H51" s="41"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="33"/>
@@ -1517,6 +1616,7 @@
       <x:c r="G52" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H52" s="41"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="33"/>
@@ -1534,6 +1634,7 @@
       <x:c r="G53" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H53" s="41"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="33"/>
@@ -1551,6 +1652,7 @@
       <x:c r="G54" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H54" s="41"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="33"/>
@@ -1568,6 +1670,7 @@
       <x:c r="G55" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H55" s="41"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="33"/>
@@ -1585,6 +1688,7 @@
       <x:c r="G56" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H56" s="41"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="33"/>
@@ -1602,6 +1706,7 @@
       <x:c r="G57" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H57" s="41"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="33"/>
@@ -1619,6 +1724,7 @@
       <x:c r="G58" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H58" s="41"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="33"/>
@@ -1636,6 +1742,7 @@
       <x:c r="G59" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H59" s="41"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="33"/>
@@ -1653,6 +1760,7 @@
       <x:c r="G60" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H60" s="41"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="33"/>
@@ -1670,6 +1778,7 @@
       <x:c r="G61" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H61" s="41"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="33"/>
@@ -1687,6 +1796,7 @@
       <x:c r="G62" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H62" s="41"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="33"/>
@@ -1704,6 +1814,7 @@
       <x:c r="G63" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H63" s="41"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="33"/>
@@ -1721,6 +1832,7 @@
       <x:c r="G64" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H64" s="41"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="33"/>
@@ -1738,6 +1850,7 @@
       <x:c r="G65" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H65" s="41"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="33"/>
@@ -1755,6 +1868,7 @@
       <x:c r="G66" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H66" s="41"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="33"/>
@@ -1772,6 +1886,7 @@
       <x:c r="G67" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H67" s="41"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="33"/>
@@ -1789,6 +1904,7 @@
       <x:c r="G68" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H68" s="41"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="33"/>
@@ -1806,6 +1922,7 @@
       <x:c r="G69" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H69" s="41"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="33"/>
@@ -1823,6 +1940,7 @@
       <x:c r="G70" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H70" s="41"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="33"/>
@@ -1840,6 +1958,7 @@
       <x:c r="G71" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H71" s="41"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="33"/>
@@ -1857,6 +1976,7 @@
       <x:c r="G72" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H72" s="41"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="33"/>
@@ -1874,6 +1994,7 @@
       <x:c r="G73" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H73" s="41"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="33"/>
@@ -1891,6 +2012,7 @@
       <x:c r="G74" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H74" s="41"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="33"/>
@@ -1908,6 +2030,7 @@
       <x:c r="G75" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H75" s="41"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="33"/>
@@ -1925,6 +2048,7 @@
       <x:c r="G76" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H76" s="41"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="33"/>
@@ -1942,6 +2066,7 @@
       <x:c r="G77" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H77" s="41"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="33"/>
@@ -1951,7 +2076,9 @@
       <x:c r="C78" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D78" s="36"/>
+      <x:c r="D78" s="36" t="n">
+        <x:v>20007</x:v>
+      </x:c>
       <x:c r="E78" s="36" t="n">
         <x:v>20003</x:v>
       </x:c>
@@ -1960,6 +2087,9 @@
       </x:c>
       <x:c r="G78" s="36" t="n">
         <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H78" s="41" t="n">
+        <x:v>20002</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -1970,7 +2100,9 @@
       <x:c r="C79" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D79" s="36"/>
+      <x:c r="D79" s="36" t="n">
+        <x:v>20008</x:v>
+      </x:c>
       <x:c r="E79" s="36"/>
       <x:c r="F79" s="33" t="str">
         <x:v>20008</x:v>
@@ -1978,6 +2110,7 @@
       <x:c r="G79" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H79" s="41"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="33"/>
@@ -1987,7 +2120,9 @@
       <x:c r="C80" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D80" s="36"/>
+      <x:c r="D80" s="36" t="n">
+        <x:v>20015</x:v>
+      </x:c>
       <x:c r="E80" s="36" t="n">
         <x:v>20011</x:v>
       </x:c>
@@ -1997,6 +2132,7 @@
       <x:c r="G80" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H80" s="41"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="33"/>
@@ -2006,7 +2142,9 @@
       <x:c r="C81" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D81" s="36"/>
+      <x:c r="D81" s="36" t="n">
+        <x:v>20016</x:v>
+      </x:c>
       <x:c r="E81" s="36"/>
       <x:c r="F81" s="33" t="str">
         <x:v>20016</x:v>
@@ -2014,6 +2152,7 @@
       <x:c r="G81" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H81" s="41"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="33"/>
@@ -2023,7 +2162,9 @@
       <x:c r="C82" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D82" s="36"/>
+      <x:c r="D82" s="36" t="n">
+        <x:v>20023</x:v>
+      </x:c>
       <x:c r="E82" s="36" t="n">
         <x:v>20019</x:v>
       </x:c>
@@ -2033,6 +2174,7 @@
       <x:c r="G82" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H82" s="41"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="33"/>
@@ -2042,7 +2184,9 @@
       <x:c r="C83" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D83" s="36"/>
+      <x:c r="D83" s="36" t="n">
+        <x:v>20030</x:v>
+      </x:c>
       <x:c r="E83" s="36" t="n">
         <x:v>20026</x:v>
       </x:c>
@@ -2052,6 +2196,7 @@
       <x:c r="G83" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H83" s="41"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="33"/>
@@ -2061,7 +2206,9 @@
       <x:c r="C84" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D84" s="36"/>
+      <x:c r="D84" s="36" t="n">
+        <x:v>20037</x:v>
+      </x:c>
       <x:c r="E84" s="36" t="n">
         <x:v>20033</x:v>
       </x:c>
@@ -2071,6 +2218,7 @@
       <x:c r="G84" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H84" s="41"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="33"/>
@@ -2080,7 +2228,9 @@
       <x:c r="C85" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D85" s="36"/>
+      <x:c r="D85" s="36" t="n">
+        <x:v>20044</x:v>
+      </x:c>
       <x:c r="E85" s="36" t="n">
         <x:v>20040</x:v>
       </x:c>
@@ -2090,6 +2240,7 @@
       <x:c r="G85" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H85" s="41"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="33"/>
@@ -2099,7 +2250,9 @@
       <x:c r="C86" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D86" s="36"/>
+      <x:c r="D86" s="36" t="n">
+        <x:v>20051</x:v>
+      </x:c>
       <x:c r="E86" s="36" t="n">
         <x:v>20047</x:v>
       </x:c>
@@ -2109,6 +2262,7 @@
       <x:c r="G86" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H86" s="41"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="33"/>
@@ -2118,7 +2272,9 @@
       <x:c r="C87" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D87" s="36"/>
+      <x:c r="D87" s="36" t="n">
+        <x:v>20058</x:v>
+      </x:c>
       <x:c r="E87" s="36" t="n">
         <x:v>20054</x:v>
       </x:c>
@@ -2128,6 +2284,7 @@
       <x:c r="G87" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H87" s="41"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="33"/>
@@ -2137,7 +2294,9 @@
       <x:c r="C88" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D88" s="36"/>
+      <x:c r="D88" s="36" t="n">
+        <x:v>20065</x:v>
+      </x:c>
       <x:c r="E88" s="36" t="n">
         <x:v>20061</x:v>
       </x:c>
@@ -2147,6 +2306,7 @@
       <x:c r="G88" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H88" s="41"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="33"/>
@@ -2156,7 +2316,9 @@
       <x:c r="C89" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D89" s="36"/>
+      <x:c r="D89" s="36" t="n">
+        <x:v>20072</x:v>
+      </x:c>
       <x:c r="E89" s="36" t="n">
         <x:v>20068</x:v>
       </x:c>
@@ -2166,6 +2328,7 @@
       <x:c r="G89" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H89" s="41"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="33"/>
@@ -2175,7 +2338,9 @@
       <x:c r="C90" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D90" s="36"/>
+      <x:c r="D90" s="36" t="n">
+        <x:v>20079</x:v>
+      </x:c>
       <x:c r="E90" s="36" t="n">
         <x:v>20075</x:v>
       </x:c>
@@ -2185,6 +2350,7 @@
       <x:c r="G90" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H90" s="41"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="33"/>
@@ -2194,7 +2360,9 @@
       <x:c r="C91" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D91" s="36"/>
+      <x:c r="D91" s="36" t="n">
+        <x:v>20086</x:v>
+      </x:c>
       <x:c r="E91" s="36" t="n">
         <x:v>20082</x:v>
       </x:c>
@@ -2204,6 +2372,7 @@
       <x:c r="G91" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H91" s="41"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="33"/>
@@ -2213,7 +2382,9 @@
       <x:c r="C92" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D92" s="36"/>
+      <x:c r="D92" s="36" t="n">
+        <x:v>20093</x:v>
+      </x:c>
       <x:c r="E92" s="36" t="n">
         <x:v>20089</x:v>
       </x:c>
@@ -2223,6 +2394,7 @@
       <x:c r="G92" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H92" s="41"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="33"/>
@@ -2232,7 +2404,9 @@
       <x:c r="C93" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D93" s="36"/>
+      <x:c r="D93" s="36" t="n">
+        <x:v>20100</x:v>
+      </x:c>
       <x:c r="E93" s="36" t="n">
         <x:v>20096</x:v>
       </x:c>
@@ -2242,6 +2416,7 @@
       <x:c r="G93" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H93" s="41"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="33"/>
@@ -2251,7 +2426,9 @@
       <x:c r="C94" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D94" s="36"/>
+      <x:c r="D94" s="36" t="n">
+        <x:v>20107</x:v>
+      </x:c>
       <x:c r="E94" s="36" t="n">
         <x:v>20103</x:v>
       </x:c>
@@ -2261,6 +2438,7 @@
       <x:c r="G94" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H94" s="41"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="33"/>
@@ -2270,7 +2448,9 @@
       <x:c r="C95" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D95" s="36"/>
+      <x:c r="D95" s="36" t="n">
+        <x:v>20114</x:v>
+      </x:c>
       <x:c r="E95" s="36" t="n">
         <x:v>20110</x:v>
       </x:c>
@@ -2280,6 +2460,7 @@
       <x:c r="G95" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H95" s="41"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="33"/>
@@ -2289,7 +2470,9 @@
       <x:c r="C96" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D96" s="36"/>
+      <x:c r="D96" s="36" t="n">
+        <x:v>20121</x:v>
+      </x:c>
       <x:c r="E96" s="36" t="n">
         <x:v>20117</x:v>
       </x:c>
@@ -2299,6 +2482,7 @@
       <x:c r="G96" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H96" s="41"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="33"/>
@@ -2308,7 +2492,9 @@
       <x:c r="C97" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D97" s="36"/>
+      <x:c r="D97" s="36" t="n">
+        <x:v>20128</x:v>
+      </x:c>
       <x:c r="E97" s="36" t="n">
         <x:v>20124</x:v>
       </x:c>
@@ -2318,6 +2504,7 @@
       <x:c r="G97" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H97" s="41"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="33"/>
@@ -2327,7 +2514,9 @@
       <x:c r="C98" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D98" s="36"/>
+      <x:c r="D98" s="36" t="n">
+        <x:v>20135</x:v>
+      </x:c>
       <x:c r="E98" s="36" t="n">
         <x:v>20131</x:v>
       </x:c>
@@ -2337,6 +2526,7 @@
       <x:c r="G98" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H98" s="41"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="33"/>
@@ -2346,7 +2536,9 @@
       <x:c r="C99" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D99" s="36"/>
+      <x:c r="D99" s="36" t="n">
+        <x:v>20142</x:v>
+      </x:c>
       <x:c r="E99" s="36" t="n">
         <x:v>20138</x:v>
       </x:c>
@@ -2356,6 +2548,7 @@
       <x:c r="G99" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H99" s="41"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="33"/>
@@ -2365,7 +2558,9 @@
       <x:c r="C100" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D100" s="36"/>
+      <x:c r="D100" s="36" t="n">
+        <x:v>20149</x:v>
+      </x:c>
       <x:c r="E100" s="36" t="n">
         <x:v>20145</x:v>
       </x:c>
@@ -2375,6 +2570,7 @@
       <x:c r="G100" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H100" s="41"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="33"/>
@@ -2384,7 +2580,9 @@
       <x:c r="C101" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D101" s="36"/>
+      <x:c r="D101" s="36" t="n">
+        <x:v>20156</x:v>
+      </x:c>
       <x:c r="E101" s="36" t="n">
         <x:v>20152</x:v>
       </x:c>
@@ -2394,6 +2592,7 @@
       <x:c r="G101" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H101" s="41"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="33"/>
@@ -2403,7 +2602,9 @@
       <x:c r="C102" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D102" s="36"/>
+      <x:c r="D102" s="36" t="n">
+        <x:v>20158</x:v>
+      </x:c>
       <x:c r="E102" s="36" t="n">
         <x:v>20157</x:v>
       </x:c>
@@ -2413,6 +2614,7 @@
       <x:c r="G102" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H102" s="41"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="33"/>
@@ -2422,7 +2624,9 @@
       <x:c r="C103" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D103" s="36"/>
+      <x:c r="D103" s="36" t="n">
+        <x:v>20165</x:v>
+      </x:c>
       <x:c r="E103" s="36" t="n">
         <x:v>20161</x:v>
       </x:c>
@@ -2432,6 +2636,7 @@
       <x:c r="G103" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H103" s="41"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="33"/>
@@ -2441,7 +2646,9 @@
       <x:c r="C104" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D104" s="36"/>
+      <x:c r="D104" s="36" t="n">
+        <x:v>20172</x:v>
+      </x:c>
       <x:c r="E104" s="36" t="n">
         <x:v>20168</x:v>
       </x:c>
@@ -2451,6 +2658,7 @@
       <x:c r="G104" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H104" s="41"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="33"/>
@@ -2460,7 +2668,9 @@
       <x:c r="C105" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D105" s="36"/>
+      <x:c r="D105" s="36" t="n">
+        <x:v>20179</x:v>
+      </x:c>
       <x:c r="E105" s="36" t="n">
         <x:v>20175</x:v>
       </x:c>
@@ -2470,6 +2680,7 @@
       <x:c r="G105" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H105" s="41"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="33"/>
@@ -2479,7 +2690,9 @@
       <x:c r="C106" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D106" s="36"/>
+      <x:c r="D106" s="36" t="n">
+        <x:v>20186</x:v>
+      </x:c>
       <x:c r="E106" s="36" t="n">
         <x:v>20182</x:v>
       </x:c>
@@ -2489,6 +2702,7 @@
       <x:c r="G106" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H106" s="41"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="33"/>
@@ -2498,7 +2712,9 @@
       <x:c r="C107" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D107" s="36"/>
+      <x:c r="D107" s="36" t="n">
+        <x:v>20193</x:v>
+      </x:c>
       <x:c r="E107" s="36" t="n">
         <x:v>20189</x:v>
       </x:c>
@@ -2508,6 +2724,7 @@
       <x:c r="G107" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H107" s="41"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="33"/>
@@ -2517,7 +2734,9 @@
       <x:c r="C108" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D108" s="36"/>
+      <x:c r="D108" s="36" t="n">
+        <x:v>20200</x:v>
+      </x:c>
       <x:c r="E108" s="36" t="n">
         <x:v>20196</x:v>
       </x:c>
@@ -2527,6 +2746,7 @@
       <x:c r="G108" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H108" s="41"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="33"/>
@@ -2536,7 +2756,9 @@
       <x:c r="C109" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D109" s="36"/>
+      <x:c r="D109" s="36" t="n">
+        <x:v>20207</x:v>
+      </x:c>
       <x:c r="E109" s="36" t="n">
         <x:v>20203</x:v>
       </x:c>
@@ -2546,6 +2768,7 @@
       <x:c r="G109" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H109" s="41"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="33"/>
@@ -2555,7 +2778,9 @@
       <x:c r="C110" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D110" s="36"/>
+      <x:c r="D110" s="36" t="n">
+        <x:v>20214</x:v>
+      </x:c>
       <x:c r="E110" s="36" t="n">
         <x:v>20210</x:v>
       </x:c>
@@ -2565,6 +2790,7 @@
       <x:c r="G110" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H110" s="41"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="33"/>
@@ -2574,7 +2800,9 @@
       <x:c r="C111" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D111" s="36"/>
+      <x:c r="D111" s="36" t="n">
+        <x:v>20221</x:v>
+      </x:c>
       <x:c r="E111" s="36" t="n">
         <x:v>20217</x:v>
       </x:c>
@@ -2584,6 +2812,7 @@
       <x:c r="G111" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H111" s="41"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="33"/>
@@ -2593,7 +2822,9 @@
       <x:c r="C112" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D112" s="36"/>
+      <x:c r="D112" s="36" t="n">
+        <x:v>20228</x:v>
+      </x:c>
       <x:c r="E112" s="36" t="n">
         <x:v>20224</x:v>
       </x:c>
@@ -2603,6 +2834,7 @@
       <x:c r="G112" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H112" s="41"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="33"/>
@@ -2612,7 +2844,9 @@
       <x:c r="C113" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D113" s="36"/>
+      <x:c r="D113" s="36" t="n">
+        <x:v>20235</x:v>
+      </x:c>
       <x:c r="E113" s="36" t="n">
         <x:v>20231</x:v>
       </x:c>
@@ -2622,6 +2856,7 @@
       <x:c r="G113" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H113" s="41"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="33"/>
@@ -2631,7 +2866,9 @@
       <x:c r="C114" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D114" s="36"/>
+      <x:c r="D114" s="36" t="n">
+        <x:v>20242</x:v>
+      </x:c>
       <x:c r="E114" s="36" t="n">
         <x:v>20238</x:v>
       </x:c>
@@ -2641,6 +2878,7 @@
       <x:c r="G114" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H114" s="41"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="33"/>
@@ -2650,7 +2888,9 @@
       <x:c r="C115" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D115" s="36"/>
+      <x:c r="D115" s="36" t="n">
+        <x:v>20249</x:v>
+      </x:c>
       <x:c r="E115" s="36" t="n">
         <x:v>20245</x:v>
       </x:c>
@@ -2660,6 +2900,7 @@
       <x:c r="G115" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H115" s="41"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="33"/>
@@ -2669,7 +2910,9 @@
       <x:c r="C116" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D116" s="36"/>
+      <x:c r="D116" s="36" t="n">
+        <x:v>20256</x:v>
+      </x:c>
       <x:c r="E116" s="36" t="n">
         <x:v>20252</x:v>
       </x:c>
@@ -2679,6 +2922,7 @@
       <x:c r="G116" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H116" s="41"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="33"/>
@@ -2688,7 +2932,9 @@
       <x:c r="C117" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D117" s="36"/>
+      <x:c r="D117" s="36" t="n">
+        <x:v>20263</x:v>
+      </x:c>
       <x:c r="E117" s="36" t="n">
         <x:v>20259</x:v>
       </x:c>
@@ -2698,6 +2944,7 @@
       <x:c r="G117" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H117" s="41"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="33"/>
@@ -2707,7 +2954,9 @@
       <x:c r="C118" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D118" s="36"/>
+      <x:c r="D118" s="36" t="n">
+        <x:v>20270</x:v>
+      </x:c>
       <x:c r="E118" s="36" t="n">
         <x:v>20266</x:v>
       </x:c>
@@ -2717,6 +2966,7 @@
       <x:c r="G118" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H118" s="41"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="33"/>
@@ -2726,7 +2976,9 @@
       <x:c r="C119" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D119" s="36"/>
+      <x:c r="D119" s="36" t="n">
+        <x:v>20271</x:v>
+      </x:c>
       <x:c r="E119" s="36"/>
       <x:c r="F119" s="33" t="str">
         <x:v>20271</x:v>
@@ -2734,6 +2986,7 @@
       <x:c r="G119" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H119" s="41"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="33"/>
@@ -2751,6 +3004,7 @@
       <x:c r="G120" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H120" s="41"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="33"/>
@@ -2760,7 +3014,9 @@
       <x:c r="C121" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D121" s="36"/>
+      <x:c r="D121" s="36" t="n">
+        <x:v>20279</x:v>
+      </x:c>
       <x:c r="E121" s="36" t="n">
         <x:v>20275</x:v>
       </x:c>
@@ -2770,6 +3026,7 @@
       <x:c r="G121" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H121" s="41"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="33"/>
@@ -2779,7 +3036,9 @@
       <x:c r="C122" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D122" s="36"/>
+      <x:c r="D122" s="36" t="n">
+        <x:v>20286</x:v>
+      </x:c>
       <x:c r="E122" s="36" t="n">
         <x:v>20282</x:v>
       </x:c>
@@ -2789,6 +3048,7 @@
       <x:c r="G122" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H122" s="41"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="33"/>
@@ -2798,7 +3058,9 @@
       <x:c r="C123" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D123" s="36"/>
+      <x:c r="D123" s="36" t="n">
+        <x:v>20293</x:v>
+      </x:c>
       <x:c r="E123" s="36" t="n">
         <x:v>20289</x:v>
       </x:c>
@@ -2808,6 +3070,7 @@
       <x:c r="G123" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H123" s="41"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="33"/>
@@ -2817,7 +3080,9 @@
       <x:c r="C124" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D124" s="36"/>
+      <x:c r="D124" s="36" t="n">
+        <x:v>20300</x:v>
+      </x:c>
       <x:c r="E124" s="36" t="n">
         <x:v>20296</x:v>
       </x:c>
@@ -2827,6 +3092,7 @@
       <x:c r="G124" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H124" s="41"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="33"/>
@@ -2836,7 +3102,9 @@
       <x:c r="C125" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D125" s="36"/>
+      <x:c r="D125" s="36" t="n">
+        <x:v>20307</x:v>
+      </x:c>
       <x:c r="E125" s="36" t="n">
         <x:v>20303</x:v>
       </x:c>
@@ -2846,6 +3114,7 @@
       <x:c r="G125" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H125" s="41"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="33"/>
@@ -2855,7 +3124,9 @@
       <x:c r="C126" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D126" s="36"/>
+      <x:c r="D126" s="36" t="n">
+        <x:v>20314</x:v>
+      </x:c>
       <x:c r="E126" s="36" t="n">
         <x:v>20310</x:v>
       </x:c>
@@ -2865,6 +3136,7 @@
       <x:c r="G126" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H126" s="41"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="33"/>
@@ -2874,7 +3146,9 @@
       <x:c r="C127" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D127" s="36"/>
+      <x:c r="D127" s="36" t="n">
+        <x:v>20321</x:v>
+      </x:c>
       <x:c r="E127" s="36" t="n">
         <x:v>20317</x:v>
       </x:c>
@@ -2884,6 +3158,7 @@
       <x:c r="G127" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H127" s="41"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="33"/>
@@ -2893,7 +3168,9 @@
       <x:c r="C128" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D128" s="36"/>
+      <x:c r="D128" s="36" t="n">
+        <x:v>20328</x:v>
+      </x:c>
       <x:c r="E128" s="36" t="n">
         <x:v>20324</x:v>
       </x:c>
@@ -2903,6 +3180,7 @@
       <x:c r="G128" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H128" s="41"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="33"/>
@@ -2912,7 +3190,9 @@
       <x:c r="C129" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D129" s="36"/>
+      <x:c r="D129" s="36" t="n">
+        <x:v>20335</x:v>
+      </x:c>
       <x:c r="E129" s="36" t="n">
         <x:v>20331</x:v>
       </x:c>
@@ -2922,6 +3202,7 @@
       <x:c r="G129" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H129" s="41"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="33"/>
@@ -2931,7 +3212,9 @@
       <x:c r="C130" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D130" s="36"/>
+      <x:c r="D130" s="36" t="n">
+        <x:v>20342</x:v>
+      </x:c>
       <x:c r="E130" s="36" t="n">
         <x:v>20338</x:v>
       </x:c>
@@ -2941,6 +3224,7 @@
       <x:c r="G130" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H130" s="41"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="33"/>
@@ -2950,7 +3234,9 @@
       <x:c r="C131" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D131" s="36"/>
+      <x:c r="D131" s="36" t="n">
+        <x:v>20349</x:v>
+      </x:c>
       <x:c r="E131" s="36" t="n">
         <x:v>20345</x:v>
       </x:c>
@@ -2960,6 +3246,7 @@
       <x:c r="G131" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H131" s="41"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="33"/>
@@ -2969,7 +3256,9 @@
       <x:c r="C132" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D132" s="36"/>
+      <x:c r="D132" s="36" t="n">
+        <x:v>20356</x:v>
+      </x:c>
       <x:c r="E132" s="36" t="n">
         <x:v>20352</x:v>
       </x:c>
@@ -2979,6 +3268,7 @@
       <x:c r="G132" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H132" s="41"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="33"/>
@@ -2988,7 +3278,9 @@
       <x:c r="C133" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D133" s="36"/>
+      <x:c r="D133" s="36" t="n">
+        <x:v>20363</x:v>
+      </x:c>
       <x:c r="E133" s="36" t="n">
         <x:v>20359</x:v>
       </x:c>
@@ -2998,6 +3290,7 @@
       <x:c r="G133" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H133" s="41"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="33"/>
@@ -3007,7 +3300,9 @@
       <x:c r="C134" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D134" s="36"/>
+      <x:c r="D134" s="36" t="n">
+        <x:v>20370</x:v>
+      </x:c>
       <x:c r="E134" s="36" t="n">
         <x:v>20366</x:v>
       </x:c>
@@ -3017,6 +3312,7 @@
       <x:c r="G134" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H134" s="41"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="33"/>
@@ -3026,7 +3322,9 @@
       <x:c r="C135" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D135" s="36"/>
+      <x:c r="D135" s="36" t="n">
+        <x:v>20377</x:v>
+      </x:c>
       <x:c r="E135" s="36" t="n">
         <x:v>20373</x:v>
       </x:c>
@@ -3036,6 +3334,7 @@
       <x:c r="G135" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H135" s="41"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="33"/>
@@ -3045,7 +3344,9 @@
       <x:c r="C136" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D136" s="36"/>
+      <x:c r="D136" s="36" t="n">
+        <x:v>20384</x:v>
+      </x:c>
       <x:c r="E136" s="36" t="n">
         <x:v>20380</x:v>
       </x:c>
@@ -3055,6 +3356,7 @@
       <x:c r="G136" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H136" s="41"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="33"/>
@@ -3064,7 +3366,9 @@
       <x:c r="C137" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D137" s="36"/>
+      <x:c r="D137" s="36" t="n">
+        <x:v>20391</x:v>
+      </x:c>
       <x:c r="E137" s="36" t="n">
         <x:v>20387</x:v>
       </x:c>
@@ -3074,6 +3378,7 @@
       <x:c r="G137" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H137" s="41"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="33"/>
@@ -3083,7 +3388,9 @@
       <x:c r="C138" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D138" s="36"/>
+      <x:c r="D138" s="36" t="n">
+        <x:v>20398</x:v>
+      </x:c>
       <x:c r="E138" s="36" t="n">
         <x:v>20394</x:v>
       </x:c>
@@ -3093,6 +3400,7 @@
       <x:c r="G138" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H138" s="41"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="33"/>
@@ -3102,7 +3410,9 @@
       <x:c r="C139" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D139" s="36"/>
+      <x:c r="D139" s="36" t="n">
+        <x:v>20405</x:v>
+      </x:c>
       <x:c r="E139" s="36" t="n">
         <x:v>20401</x:v>
       </x:c>
@@ -3112,6 +3422,7 @@
       <x:c r="G139" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H139" s="41"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="33"/>
@@ -3121,7 +3432,9 @@
       <x:c r="C140" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D140" s="36"/>
+      <x:c r="D140" s="36" t="n">
+        <x:v>20412</x:v>
+      </x:c>
       <x:c r="E140" s="36" t="n">
         <x:v>20408</x:v>
       </x:c>
@@ -3131,6 +3444,7 @@
       <x:c r="G140" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H140" s="41"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="33"/>
@@ -3140,7 +3454,9 @@
       <x:c r="C141" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D141" s="36"/>
+      <x:c r="D141" s="36" t="n">
+        <x:v>20419</x:v>
+      </x:c>
       <x:c r="E141" s="36" t="n">
         <x:v>20415</x:v>
       </x:c>
@@ -3150,6 +3466,7 @@
       <x:c r="G141" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H141" s="41"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="33"/>
@@ -3159,7 +3476,9 @@
       <x:c r="C142" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D142" s="36"/>
+      <x:c r="D142" s="36" t="n">
+        <x:v>20426</x:v>
+      </x:c>
       <x:c r="E142" s="36" t="n">
         <x:v>20422</x:v>
       </x:c>
@@ -3169,6 +3488,7 @@
       <x:c r="G142" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H142" s="41"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="33"/>
@@ -3178,7 +3498,9 @@
       <x:c r="C143" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D143" s="36"/>
+      <x:c r="D143" s="36" t="n">
+        <x:v>20433</x:v>
+      </x:c>
       <x:c r="E143" s="36" t="n">
         <x:v>20429</x:v>
       </x:c>
@@ -3188,6 +3510,7 @@
       <x:c r="G143" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H143" s="41"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="33"/>
@@ -3197,7 +3520,9 @@
       <x:c r="C144" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D144" s="36"/>
+      <x:c r="D144" s="36" t="n">
+        <x:v>20440</x:v>
+      </x:c>
       <x:c r="E144" s="36" t="n">
         <x:v>20436</x:v>
       </x:c>
@@ -3207,6 +3532,7 @@
       <x:c r="G144" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H144" s="41"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="33"/>
@@ -3216,7 +3542,9 @@
       <x:c r="C145" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D145" s="36"/>
+      <x:c r="D145" s="36" t="n">
+        <x:v>20447</x:v>
+      </x:c>
       <x:c r="E145" s="36" t="n">
         <x:v>20443</x:v>
       </x:c>
@@ -3226,6 +3554,7 @@
       <x:c r="G145" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H145" s="41"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="33"/>
@@ -3235,7 +3564,9 @@
       <x:c r="C146" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D146" s="36"/>
+      <x:c r="D146" s="36" t="n">
+        <x:v>20454</x:v>
+      </x:c>
       <x:c r="E146" s="36" t="n">
         <x:v>20450</x:v>
       </x:c>
@@ -3245,6 +3576,7 @@
       <x:c r="G146" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H146" s="41"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="33"/>
@@ -3254,7 +3586,9 @@
       <x:c r="C147" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D147" s="36"/>
+      <x:c r="D147" s="36" t="n">
+        <x:v>20461</x:v>
+      </x:c>
       <x:c r="E147" s="36" t="n">
         <x:v>20457</x:v>
       </x:c>
@@ -3264,6 +3598,7 @@
       <x:c r="G147" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H147" s="41"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="33"/>
@@ -3273,7 +3608,9 @@
       <x:c r="C148" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D148" s="36"/>
+      <x:c r="D148" s="36" t="n">
+        <x:v>20468</x:v>
+      </x:c>
       <x:c r="E148" s="36" t="n">
         <x:v>20464</x:v>
       </x:c>
@@ -3283,6 +3620,7 @@
       <x:c r="G148" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H148" s="41"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="33"/>
@@ -3292,7 +3630,9 @@
       <x:c r="C149" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D149" s="36"/>
+      <x:c r="D149" s="36" t="n">
+        <x:v>20475</x:v>
+      </x:c>
       <x:c r="E149" s="36" t="n">
         <x:v>20471</x:v>
       </x:c>
@@ -3302,6 +3642,7 @@
       <x:c r="G149" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H149" s="41"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="33"/>
@@ -3311,7 +3652,9 @@
       <x:c r="C150" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D150" s="36"/>
+      <x:c r="D150" s="36" t="n">
+        <x:v>20482</x:v>
+      </x:c>
       <x:c r="E150" s="36" t="n">
         <x:v>20478</x:v>
       </x:c>
@@ -3321,6 +3664,7 @@
       <x:c r="G150" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H150" s="41"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="33"/>
@@ -3330,7 +3674,9 @@
       <x:c r="C151" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D151" s="36"/>
+      <x:c r="D151" s="36" t="n">
+        <x:v>20489</x:v>
+      </x:c>
       <x:c r="E151" s="36" t="n">
         <x:v>20485</x:v>
       </x:c>
@@ -3340,6 +3686,7 @@
       <x:c r="G151" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H151" s="41"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="33"/>
@@ -3349,7 +3696,9 @@
       <x:c r="C152" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D152" s="36"/>
+      <x:c r="D152" s="36" t="n">
+        <x:v>20490</x:v>
+      </x:c>
       <x:c r="E152" s="36"/>
       <x:c r="F152" s="33" t="str">
         <x:v>20490</x:v>
@@ -3357,6 +3706,7 @@
       <x:c r="G152" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H152" s="41"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="33"/>
@@ -3366,7 +3716,9 @@
       <x:c r="C153" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D153" s="36"/>
+      <x:c r="D153" s="36" t="n">
+        <x:v>20497</x:v>
+      </x:c>
       <x:c r="E153" s="36" t="n">
         <x:v>20493</x:v>
       </x:c>
@@ -3376,6 +3728,7 @@
       <x:c r="G153" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H153" s="41"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="33"/>
@@ -3385,7 +3738,9 @@
       <x:c r="C154" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D154" s="36"/>
+      <x:c r="D154" s="36" t="n">
+        <x:v>20504</x:v>
+      </x:c>
       <x:c r="E154" s="36" t="n">
         <x:v>20500</x:v>
       </x:c>
@@ -3395,6 +3750,7 @@
       <x:c r="G154" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H154" s="41"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="33"/>
@@ -3404,7 +3760,9 @@
       <x:c r="C155" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D155" s="36"/>
+      <x:c r="D155" s="36" t="n">
+        <x:v>20511</x:v>
+      </x:c>
       <x:c r="E155" s="36" t="n">
         <x:v>20507</x:v>
       </x:c>
@@ -3414,6 +3772,7 @@
       <x:c r="G155" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H155" s="41"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="33"/>
@@ -3423,7 +3782,9 @@
       <x:c r="C156" s="33" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="D156" s="36"/>
+      <x:c r="D156" s="36" t="n">
+        <x:v>20512</x:v>
+      </x:c>
       <x:c r="E156" s="36"/>
       <x:c r="F156" s="33" t="str">
         <x:v>20512</x:v>
@@ -3431,6 +3792,7 @@
       <x:c r="G156" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H156" s="41"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="33"/>
@@ -3448,6 +3810,7 @@
       <x:c r="G157" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H157" s="41"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="33"/>
@@ -3465,6 +3828,7 @@
       <x:c r="G158" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H158" s="41"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="33"/>
@@ -3482,6 +3846,7 @@
       <x:c r="G159" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H159" s="41"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="33"/>
@@ -3499,6 +3864,7 @@
       <x:c r="G160" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H160" s="41"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="33"/>
@@ -3516,6 +3882,7 @@
       <x:c r="G161" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H161" s="41"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="33"/>
@@ -3533,6 +3900,7 @@
       <x:c r="G162" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H162" s="41"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="33"/>
@@ -3550,6 +3918,7 @@
       <x:c r="G163" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H163" s="41"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="33"/>
@@ -3567,6 +3936,7 @@
       <x:c r="G164" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H164" s="41"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="33"/>
@@ -3584,6 +3954,7 @@
       <x:c r="G165" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H165" s="41"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="33"/>
@@ -3601,6 +3972,7 @@
       <x:c r="G166" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H166" s="41"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="33"/>
@@ -3618,6 +3990,7 @@
       <x:c r="G167" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H167" s="41"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="33"/>
@@ -3635,6 +4008,7 @@
       <x:c r="G168" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H168" s="41"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="33"/>
@@ -3652,6 +4026,7 @@
       <x:c r="G169" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H169" s="41"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="33"/>
@@ -3669,6 +4044,7 @@
       <x:c r="G170" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H170" s="41"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="33"/>
@@ -3686,6 +4062,7 @@
       <x:c r="G171" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H171" s="41"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="33"/>
@@ -3703,6 +4080,7 @@
       <x:c r="G172" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H172" s="41"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="33"/>
@@ -3720,6 +4098,7 @@
       <x:c r="G173" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H173" s="41"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="33"/>
@@ -3737,6 +4116,7 @@
       <x:c r="G174" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H174" s="41"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="33"/>
@@ -3754,6 +4134,7 @@
       <x:c r="G175" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H175" s="41"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="33"/>
@@ -3771,6 +4152,7 @@
       <x:c r="G176" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H176" s="41"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="33"/>
@@ -3788,6 +4170,7 @@
       <x:c r="G177" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H177" s="41"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="33"/>
@@ -3805,6 +4188,7 @@
       <x:c r="G178" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H178" s="41"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="33"/>
@@ -3822,6 +4206,7 @@
       <x:c r="G179" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H179" s="41"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="33"/>
@@ -3839,6 +4224,7 @@
       <x:c r="G180" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H180" s="41"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="33"/>
@@ -3856,6 +4242,7 @@
       <x:c r="G181" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H181" s="41"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="33"/>
@@ -3873,6 +4260,7 @@
       <x:c r="G182" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H182" s="41"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="33"/>
@@ -3890,6 +4278,7 @@
       <x:c r="G183" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H183" s="41"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="33"/>
@@ -3907,6 +4296,7 @@
       <x:c r="G184" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H184" s="41"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="33"/>
@@ -3924,6 +4314,7 @@
       <x:c r="G185" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H185" s="41"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="33"/>
@@ -3941,6 +4332,7 @@
       <x:c r="G186" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H186" s="41"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="33"/>
@@ -3958,6 +4350,7 @@
       <x:c r="G187" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H187" s="41"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="33"/>
@@ -3975,6 +4368,7 @@
       <x:c r="G188" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H188" s="41"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="33"/>
@@ -3992,6 +4386,7 @@
       <x:c r="G189" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H189" s="41"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="33"/>
@@ -4009,6 +4404,7 @@
       <x:c r="G190" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H190" s="41"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="33"/>
@@ -4026,6 +4422,7 @@
       <x:c r="G191" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H191" s="41"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="33"/>
@@ -4043,6 +4440,7 @@
       <x:c r="G192" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H192" s="41"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="33"/>
@@ -4060,6 +4458,7 @@
       <x:c r="G193" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H193" s="41"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="33"/>
@@ -4077,6 +4476,7 @@
       <x:c r="G194" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H194" s="41"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="33"/>
@@ -4094,6 +4494,7 @@
       <x:c r="G195" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H195" s="41"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="33"/>
@@ -4111,6 +4512,7 @@
       <x:c r="G196" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H196" s="41"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="33"/>
@@ -4128,6 +4530,7 @@
       <x:c r="G197" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H197" s="41"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="33"/>
@@ -4145,6 +4548,7 @@
       <x:c r="G198" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H198" s="41"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="33"/>
@@ -4162,6 +4566,7 @@
       <x:c r="G199" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H199" s="41"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="33"/>
@@ -4179,6 +4584,7 @@
       <x:c r="G200" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H200" s="41"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="33"/>
@@ -4196,6 +4602,7 @@
       <x:c r="G201" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H201" s="41"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="33"/>
@@ -4213,6 +4620,7 @@
       <x:c r="G202" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H202" s="41"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="33"/>
@@ -4230,6 +4638,7 @@
       <x:c r="G203" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H203" s="41"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="33"/>
@@ -4247,6 +4656,7 @@
       <x:c r="G204" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H204" s="41"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="33"/>
@@ -4264,6 +4674,7 @@
       <x:c r="G205" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H205" s="41"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="33"/>
@@ -4281,6 +4692,7 @@
       <x:c r="G206" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H206" s="41"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="33"/>
@@ -4298,6 +4710,7 @@
       <x:c r="G207" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H207" s="41"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="33"/>
@@ -4315,6 +4728,7 @@
       <x:c r="G208" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H208" s="41"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="33"/>
@@ -4332,6 +4746,7 @@
       <x:c r="G209" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H209" s="41"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="33"/>
@@ -4349,6 +4764,7 @@
       <x:c r="G210" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H210" s="41"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="33"/>
@@ -4366,6 +4782,7 @@
       <x:c r="G211" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H211" s="41"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="33"/>
@@ -4383,6 +4800,7 @@
       <x:c r="G212" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H212" s="41"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="33"/>
@@ -4400,6 +4818,7 @@
       <x:c r="G213" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H213" s="41"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="33"/>
@@ -4417,6 +4836,7 @@
       <x:c r="G214" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H214" s="41"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="33"/>
@@ -4434,6 +4854,7 @@
       <x:c r="G215" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H215" s="41"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="33"/>
@@ -4451,6 +4872,7 @@
       <x:c r="G216" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H216" s="41"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="33"/>
@@ -4468,6 +4890,7 @@
       <x:c r="G217" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H217" s="41"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="33"/>
@@ -4485,6 +4908,7 @@
       <x:c r="G218" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H218" s="41"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="33"/>
@@ -4502,6 +4926,7 @@
       <x:c r="G219" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H219" s="41"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="33"/>
@@ -4519,6 +4944,7 @@
       <x:c r="G220" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H220" s="41"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="33"/>
@@ -4536,6 +4962,7 @@
       <x:c r="G221" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H221" s="41"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="33"/>
@@ -4553,6 +4980,7 @@
       <x:c r="G222" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H222" s="41"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="33"/>
@@ -4570,6 +4998,7 @@
       <x:c r="G223" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H223" s="41"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="33"/>
@@ -4587,6 +5016,7 @@
       <x:c r="G224" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H224" s="41"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="33"/>
@@ -4604,6 +5034,7 @@
       <x:c r="G225" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H225" s="41"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="33"/>
@@ -4621,6 +5052,7 @@
       <x:c r="G226" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H226" s="41"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="33"/>
@@ -4638,6 +5070,7 @@
       <x:c r="G227" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H227" s="41"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="33"/>
@@ -4655,6 +5088,7 @@
       <x:c r="G228" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H228" s="41"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="33"/>
@@ -4672,6 +5106,7 @@
       <x:c r="G229" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H229" s="41"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="33"/>
@@ -4689,6 +5124,7 @@
       <x:c r="G230" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H230" s="41"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="33"/>
@@ -4706,6 +5142,7 @@
       <x:c r="G231" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H231" s="41"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="33"/>
@@ -4723,6 +5160,7 @@
       <x:c r="G232" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H232" s="41"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="33"/>
@@ -4740,6 +5178,7 @@
       <x:c r="G233" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H233" s="41"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="33"/>
@@ -4757,6 +5196,7 @@
       <x:c r="G234" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H234" s="41"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="33"/>
@@ -4774,6 +5214,7 @@
       <x:c r="G235" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H235" s="41"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="33"/>
@@ -4791,6 +5232,7 @@
       <x:c r="G236" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H236" s="41"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="33"/>
@@ -4808,6 +5250,7 @@
       <x:c r="G237" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H237" s="41"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="33"/>
@@ -4825,6 +5268,7 @@
       <x:c r="G238" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H238" s="41"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="33"/>
@@ -4842,6 +5286,7 @@
       <x:c r="G239" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H239" s="41"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="33"/>
@@ -4859,6 +5304,7 @@
       <x:c r="G240" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H240" s="41"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="33"/>
@@ -4876,6 +5322,7 @@
       <x:c r="G241" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H241" s="41"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="33"/>
@@ -4893,6 +5340,7 @@
       <x:c r="G242" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H242" s="41"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="33"/>
@@ -4910,6 +5358,7 @@
       <x:c r="G243" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H243" s="41"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="33"/>
@@ -4927,6 +5376,7 @@
       <x:c r="G244" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H244" s="41"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="33"/>
@@ -4944,6 +5394,7 @@
       <x:c r="G245" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H245" s="41"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="33"/>
@@ -4961,6 +5412,7 @@
       <x:c r="G246" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H246" s="41"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="33"/>
@@ -4978,6 +5430,7 @@
       <x:c r="G247" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H247" s="41"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="33"/>
@@ -4995,6 +5448,7 @@
       <x:c r="G248" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H248" s="41"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="33"/>
@@ -5012,6 +5466,7 @@
       <x:c r="G249" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H249" s="41"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="33"/>
@@ -5029,6 +5484,7 @@
       <x:c r="G250" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H250" s="41"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="33"/>
@@ -5046,6 +5502,7 @@
       <x:c r="G251" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H251" s="41"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="33"/>
@@ -5063,6 +5520,7 @@
       <x:c r="G252" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H252" s="41"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="33"/>
@@ -5080,6 +5538,7 @@
       <x:c r="G253" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H253" s="41"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="33"/>
@@ -5097,6 +5556,7 @@
       <x:c r="G254" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H254" s="41"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="33"/>
@@ -5114,6 +5574,7 @@
       <x:c r="G255" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H255" s="41"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="33"/>
@@ -5131,6 +5592,7 @@
       <x:c r="G256" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H256" s="41"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="33"/>
@@ -5148,6 +5610,7 @@
       <x:c r="G257" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H257" s="41"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="33"/>
@@ -5165,6 +5628,7 @@
       <x:c r="G258" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H258" s="41"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="33"/>
@@ -5182,6 +5646,7 @@
       <x:c r="G259" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H259" s="41"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="33"/>
@@ -5199,6 +5664,7 @@
       <x:c r="G260" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H260" s="41"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="33"/>
@@ -5216,6 +5682,7 @@
       <x:c r="G261" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H261" s="41"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="33"/>
@@ -5233,6 +5700,7 @@
       <x:c r="G262" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H262" s="41"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="33"/>
@@ -5250,6 +5718,7 @@
       <x:c r="G263" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H263" s="41"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="33"/>
@@ -5267,6 +5736,7 @@
       <x:c r="G264" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H264" s="41"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="33"/>
@@ -5284,6 +5754,7 @@
       <x:c r="G265" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H265" s="41"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="33"/>
@@ -5301,6 +5772,7 @@
       <x:c r="G266" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H266" s="41"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="33"/>
@@ -5318,6 +5790,7 @@
       <x:c r="G267" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H267" s="41"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="33"/>
@@ -5335,6 +5808,7 @@
       <x:c r="G268" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H268" s="41"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="33"/>
@@ -5352,6 +5826,7 @@
       <x:c r="G269" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H269" s="41"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="33"/>
@@ -5369,6 +5844,7 @@
       <x:c r="G270" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H270" s="41"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="33"/>
@@ -5386,6 +5862,7 @@
       <x:c r="G271" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H271" s="41"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="33"/>
@@ -5403,6 +5880,7 @@
       <x:c r="G272" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H272" s="41"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="33"/>
@@ -5420,6 +5898,7 @@
       <x:c r="G273" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H273" s="41"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="33"/>
@@ -5437,6 +5916,7 @@
       <x:c r="G274" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H274" s="41"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="33"/>
@@ -5454,6 +5934,7 @@
       <x:c r="G275" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H275" s="41"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="33"/>
@@ -5471,6 +5952,7 @@
       <x:c r="G276" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H276" s="41"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="33"/>
@@ -5488,6 +5970,7 @@
       <x:c r="G277" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H277" s="41"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="33"/>
@@ -5505,6 +5988,7 @@
       <x:c r="G278" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H278" s="41"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="33"/>
@@ -5522,6 +6006,7 @@
       <x:c r="G279" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H279" s="41"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="33"/>
@@ -5539,6 +6024,7 @@
       <x:c r="G280" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H280" s="41"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="33"/>
@@ -5556,6 +6042,7 @@
       <x:c r="G281" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H281" s="41"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="33"/>
@@ -5573,6 +6060,7 @@
       <x:c r="G282" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H282" s="41"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="33"/>
@@ -5590,6 +6078,7 @@
       <x:c r="G283" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H283" s="41"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="33"/>
@@ -5607,6 +6096,7 @@
       <x:c r="G284" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H284" s="41"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="33"/>
@@ -5624,6 +6114,7 @@
       <x:c r="G285" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H285" s="41"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="33"/>
@@ -5641,6 +6132,7 @@
       <x:c r="G286" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H286" s="41"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="33"/>
@@ -5658,6 +6150,7 @@
       <x:c r="G287" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H287" s="41"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="33"/>
@@ -5675,6 +6168,7 @@
       <x:c r="G288" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H288" s="41"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="33"/>
@@ -5692,6 +6186,7 @@
       <x:c r="G289" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H289" s="41"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="33"/>
@@ -5709,6 +6204,7 @@
       <x:c r="G290" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H290" s="41"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="33"/>
@@ -5726,6 +6222,7 @@
       <x:c r="G291" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H291" s="41"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="33"/>
@@ -5743,6 +6240,7 @@
       <x:c r="G292" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H292" s="41"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="33"/>
@@ -5760,6 +6258,7 @@
       <x:c r="G293" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H293" s="41"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="33"/>
@@ -5777,6 +6276,7 @@
       <x:c r="G294" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H294" s="41"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="33"/>
@@ -5794,6 +6294,7 @@
       <x:c r="G295" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H295" s="41"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="33"/>
@@ -5811,6 +6312,7 @@
       <x:c r="G296" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H296" s="41"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="33"/>
@@ -5828,6 +6330,7 @@
       <x:c r="G297" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H297" s="41"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="33"/>
@@ -5845,6 +6348,7 @@
       <x:c r="G298" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H298" s="41"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="33"/>
@@ -5862,6 +6366,7 @@
       <x:c r="G299" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H299" s="41"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="33"/>
@@ -5879,6 +6384,7 @@
       <x:c r="G300" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H300" s="41"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="33"/>
@@ -5896,6 +6402,7 @@
       <x:c r="G301" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H301" s="41"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="33"/>
@@ -5913,6 +6420,7 @@
       <x:c r="G302" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H302" s="41"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="33"/>
@@ -5930,6 +6438,7 @@
       <x:c r="G303" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H303" s="41"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="33"/>
@@ -5947,6 +6456,7 @@
       <x:c r="G304" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H304" s="41"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="33"/>
@@ -5964,6 +6474,7 @@
       <x:c r="G305" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H305" s="41"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="33"/>
@@ -5981,6 +6492,7 @@
       <x:c r="G306" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H306" s="41"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="33"/>
@@ -5998,6 +6510,7 @@
       <x:c r="G307" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H307" s="41"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="33"/>
@@ -6015,6 +6528,7 @@
       <x:c r="G308" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H308" s="41"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="33"/>
@@ -6032,6 +6546,7 @@
       <x:c r="G309" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H309" s="41"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="33"/>
@@ -6049,6 +6564,7 @@
       <x:c r="G310" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H310" s="41"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="33"/>
@@ -6066,6 +6582,7 @@
       <x:c r="G311" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H311" s="41"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="33"/>
@@ -6083,6 +6600,7 @@
       <x:c r="G312" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H312" s="41"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="33"/>
@@ -6100,6 +6618,7 @@
       <x:c r="G313" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H313" s="41"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="33"/>
@@ -6117,6 +6636,7 @@
       <x:c r="G314" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H314" s="41"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="33"/>
@@ -6134,6 +6654,7 @@
       <x:c r="G315" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H315" s="41"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="33"/>
@@ -6151,6 +6672,7 @@
       <x:c r="G316" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H316" s="41"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="33"/>
@@ -6168,6 +6690,7 @@
       <x:c r="G317" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H317" s="41"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="33"/>
@@ -6185,6 +6708,7 @@
       <x:c r="G318" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H318" s="41"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="33"/>
@@ -6202,6 +6726,7 @@
       <x:c r="G319" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H319" s="41"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="33"/>
@@ -6219,6 +6744,7 @@
       <x:c r="G320" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H320" s="41"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="33"/>
@@ -6236,6 +6762,7 @@
       <x:c r="G321" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H321" s="41"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="33"/>
@@ -6253,6 +6780,7 @@
       <x:c r="G322" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H322" s="41"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="33"/>
@@ -6270,6 +6798,7 @@
       <x:c r="G323" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H323" s="41"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="33"/>
@@ -6287,6 +6816,7 @@
       <x:c r="G324" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H324" s="41"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="33"/>
@@ -6304,6 +6834,7 @@
       <x:c r="G325" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H325" s="41"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="33"/>
@@ -6321,6 +6852,7 @@
       <x:c r="G326" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H326" s="41"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="33"/>
@@ -6338,6 +6870,7 @@
       <x:c r="G327" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H327" s="41"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="33"/>
@@ -6355,6 +6888,7 @@
       <x:c r="G328" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H328" s="41"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="33"/>
@@ -6372,6 +6906,7 @@
       <x:c r="G329" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H329" s="41"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="33"/>
@@ -6389,6 +6924,7 @@
       <x:c r="G330" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H330" s="41"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="33"/>
@@ -6406,6 +6942,7 @@
       <x:c r="G331" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H331" s="41"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="33"/>
@@ -6423,6 +6960,7 @@
       <x:c r="G332" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H332" s="41"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="33"/>
@@ -6440,6 +6978,7 @@
       <x:c r="G333" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H333" s="41"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="33"/>
@@ -6457,6 +6996,7 @@
       <x:c r="G334" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H334" s="41"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="33"/>
@@ -6474,6 +7014,7 @@
       <x:c r="G335" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H335" s="41"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="33"/>
@@ -6491,6 +7032,7 @@
       <x:c r="G336" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H336" s="41"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="33"/>
@@ -6508,6 +7050,7 @@
       <x:c r="G337" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H337" s="41"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="33"/>
@@ -6525,6 +7068,7 @@
       <x:c r="G338" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H338" s="41"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="33"/>
@@ -6542,6 +7086,7 @@
       <x:c r="G339" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H339" s="41"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="33"/>
@@ -6559,6 +7104,7 @@
       <x:c r="G340" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H340" s="41"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="33"/>
@@ -6576,6 +7122,7 @@
       <x:c r="G341" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H341" s="41"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="33"/>
@@ -6593,6 +7140,7 @@
       <x:c r="G342" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H342" s="41"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="33"/>
@@ -6610,6 +7158,7 @@
       <x:c r="G343" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H343" s="41"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="33"/>
@@ -6627,6 +7176,7 @@
       <x:c r="G344" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H344" s="41"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="33"/>
@@ -6644,6 +7194,7 @@
       <x:c r="G345" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H345" s="41"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="33"/>
@@ -6661,6 +7212,7 @@
       <x:c r="G346" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H346" s="41"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="33"/>
@@ -6678,6 +7230,7 @@
       <x:c r="G347" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H347" s="41"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="34"/>
@@ -6695,6 +7248,7 @@
       <x:c r="G348" s="37" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H348" s="41"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/b_表现集合_VisualSetConfig.xlsx
+++ b/Config/Datas/Tables/b_表现集合_VisualSetConfig.xlsx
@@ -1021,7 +1021,7 @@
           <t>10001;10002;10003;10004;10005;10006;10007;10008;10009</t>
         </is>
       </c>
-      <c r="G5" s="95" t="n">
+      <c r="G5" s="95">
         <v>1000</v>
       </c>
       <c r="H5" s="66" t="n"/>
@@ -1173,7 +1173,7 @@
           <t>10047;10048;10049;10050;10051;10052;10053;10054;10055</t>
         </is>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="G11" s="95">
         <v>1000</v>
       </c>
       <c r="H11" s="66" t="n"/>
@@ -1303,7 +1303,7 @@
           <t>10092;10093;10094;10095;10096;10097;10098;10099;10100</t>
         </is>
       </c>
-      <c r="G16" s="95" t="n">
+      <c r="G16" s="95">
         <v>1000</v>
       </c>
       <c r="H16" s="66" t="n"/>
@@ -1433,7 +1433,7 @@
           <t>10137;10138;10139;10140;10141;10142;10143;10144;10145;10146</t>
         </is>
       </c>
-      <c r="G21" s="95" t="n">
+      <c r="G21" s="95">
         <v>1000</v>
       </c>
       <c r="H21" s="66" t="n"/>
@@ -1563,7 +1563,7 @@
           <t>10184;10185;10186;10187;10188;10189;10190;10191;10192</t>
         </is>
       </c>
-      <c r="G26" s="95" t="n">
+      <c r="G26" s="95">
         <v>1000</v>
       </c>
       <c r="H26" s="66" t="n"/>
@@ -1693,7 +1693,7 @@
           <t>10229;10230;10231;10232;10233;10234;10235;10236;10237</t>
         </is>
       </c>
-      <c r="G31" s="95" t="n">
+      <c r="G31" s="95">
         <v>1000</v>
       </c>
       <c r="H31" s="66" t="n"/>
@@ -2747,7 +2747,7 @@
           <t>20001;20002;20003;20004;20005;20006;20007</t>
         </is>
       </c>
-      <c r="G78" s="95" t="n">
+      <c r="G78" s="95">
         <v>1000</v>
       </c>
       <c r="H78" s="66" t="n">
@@ -2773,7 +2773,7 @@
           <t>20008</t>
         </is>
       </c>
-      <c r="G79" s="95" t="n">
+      <c r="G79" s="95">
         <v>1000</v>
       </c>
       <c r="H79" s="66" t="n"/>
@@ -2799,7 +2799,7 @@
           <t>20009;20010;20011;20012;20013;20014;20015</t>
         </is>
       </c>
-      <c r="G80" s="95" t="n">
+      <c r="G80" s="95">
         <v>1000</v>
       </c>
       <c r="H80" s="66" t="n"/>
@@ -2823,7 +2823,7 @@
           <t>20016</t>
         </is>
       </c>
-      <c r="G81" s="95" t="n">
+      <c r="G81" s="95">
         <v>1000</v>
       </c>
       <c r="H81" s="66" t="n"/>
@@ -2849,7 +2849,7 @@
           <t>20017;20018;20019;20020;20021;20022;20023</t>
         </is>
       </c>
-      <c r="G82" s="95" t="n">
+      <c r="G82" s="95">
         <v>1000</v>
       </c>
       <c r="H82" s="66" t="n"/>
@@ -2875,7 +2875,7 @@
           <t>20024;20025;20026;20027;20028;20029;20030</t>
         </is>
       </c>
-      <c r="G83" s="95" t="n">
+      <c r="G83" s="95">
         <v>1000</v>
       </c>
       <c r="H83" s="66" t="n"/>
@@ -2901,7 +2901,7 @@
           <t>20031;20032;20033;20034;20035;20036;20037</t>
         </is>
       </c>
-      <c r="G84" s="95" t="n">
+      <c r="G84" s="95">
         <v>1000</v>
       </c>
       <c r="H84" s="66" t="n"/>
@@ -2927,7 +2927,7 @@
           <t>20038;20039;20040;20041;20042;20043;20044</t>
         </is>
       </c>
-      <c r="G85" s="95" t="n">
+      <c r="G85" s="95">
         <v>1000</v>
       </c>
       <c r="H85" s="66" t="n"/>
@@ -2953,7 +2953,7 @@
           <t>20045;20046;20047;20048;20049;20050;20051</t>
         </is>
       </c>
-      <c r="G86" s="95" t="n">
+      <c r="G86" s="95">
         <v>1000</v>
       </c>
       <c r="H86" s="66" t="n"/>
@@ -2979,7 +2979,7 @@
           <t>20052;20053;20054;20055;20056;20057;20058</t>
         </is>
       </c>
-      <c r="G87" s="95" t="n">
+      <c r="G87" s="95">
         <v>1000</v>
       </c>
       <c r="H87" s="66" t="n">
@@ -3007,7 +3007,7 @@
           <t>20059;20060;20061;20062;20063;20064;20065</t>
         </is>
       </c>
-      <c r="G88" s="95" t="n">
+      <c r="G88" s="95">
         <v>1000</v>
       </c>
       <c r="H88" s="66" t="n">
@@ -3035,7 +3035,7 @@
           <t>20066;20067;20068;20069;20070;20071;20072</t>
         </is>
       </c>
-      <c r="G89" s="95" t="n">
+      <c r="G89" s="95">
         <v>1000</v>
       </c>
       <c r="H89" s="66" t="n">
@@ -3063,7 +3063,7 @@
           <t>20073;20074;20075;20076;20077;20078;20079</t>
         </is>
       </c>
-      <c r="G90" s="95" t="n">
+      <c r="G90" s="95">
         <v>1000</v>
       </c>
       <c r="H90" s="66" t="n">
@@ -3091,7 +3091,7 @@
           <t>20080;20081;20082;20083;20084;20085;20086</t>
         </is>
       </c>
-      <c r="G91" s="95" t="n">
+      <c r="G91" s="95">
         <v>1000</v>
       </c>
       <c r="H91" s="66" t="n"/>
@@ -3117,7 +3117,7 @@
           <t>20087;20088;20089;20090;20091;20092;20093</t>
         </is>
       </c>
-      <c r="G92" s="95" t="n">
+      <c r="G92" s="95">
         <v>1000</v>
       </c>
       <c r="H92" s="66" t="n"/>
@@ -3143,7 +3143,7 @@
           <t>20094;20095;20096;20097;20098;20099;20100</t>
         </is>
       </c>
-      <c r="G93" s="95" t="n">
+      <c r="G93" s="95">
         <v>1000</v>
       </c>
       <c r="H93" s="66" t="n"/>
@@ -3169,7 +3169,7 @@
           <t>20101;20102;20103;20104;20105;20106;20107</t>
         </is>
       </c>
-      <c r="G94" s="95" t="n">
+      <c r="G94" s="95">
         <v>1000</v>
       </c>
       <c r="H94" s="66" t="n"/>
@@ -3195,7 +3195,7 @@
           <t>20108;20109;20110;20111;20112;20113;20114</t>
         </is>
       </c>
-      <c r="G95" s="95" t="n">
+      <c r="G95" s="95">
         <v>1000</v>
       </c>
       <c r="H95" s="66" t="n"/>
@@ -3221,7 +3221,7 @@
           <t>20115;20116;20117;20118;20119;20120;20121</t>
         </is>
       </c>
-      <c r="G96" s="95" t="n">
+      <c r="G96" s="95">
         <v>1000</v>
       </c>
       <c r="H96" s="66" t="n"/>
@@ -3247,7 +3247,7 @@
           <t>20122;20123;20124;20125;20126;20127;20128</t>
         </is>
       </c>
-      <c r="G97" s="95" t="n">
+      <c r="G97" s="95">
         <v>1000</v>
       </c>
       <c r="H97" s="66" t="n"/>
@@ -3273,7 +3273,7 @@
           <t>20129;20130;20131;20132;20133;20134;20135</t>
         </is>
       </c>
-      <c r="G98" s="95" t="n">
+      <c r="G98" s="95">
         <v>1000</v>
       </c>
       <c r="H98" s="66" t="n"/>
@@ -3299,7 +3299,7 @@
           <t>20136;20137;20138;20139;20140;20141;20142</t>
         </is>
       </c>
-      <c r="G99" s="95" t="n">
+      <c r="G99" s="95">
         <v>1000</v>
       </c>
       <c r="H99" s="66" t="n"/>
@@ -3325,7 +3325,7 @@
           <t>20143;20144;20145;20146;20147;20148;20149</t>
         </is>
       </c>
-      <c r="G100" s="95" t="n">
+      <c r="G100" s="95">
         <v>1000</v>
       </c>
       <c r="H100" s="66" t="n"/>
@@ -3351,7 +3351,7 @@
           <t>20150;20151;20152;20153;20154;20155;20156</t>
         </is>
       </c>
-      <c r="G101" s="95" t="n">
+      <c r="G101" s="95">
         <v>1000</v>
       </c>
       <c r="H101" s="66" t="n"/>
@@ -3377,7 +3377,7 @@
           <t>20157;20158</t>
         </is>
       </c>
-      <c r="G102" s="95" t="n">
+      <c r="G102" s="95">
         <v>1000</v>
       </c>
       <c r="H102" s="66" t="n"/>
@@ -3403,7 +3403,7 @@
           <t>20159;20160;20161;20162;20163;20164;20165</t>
         </is>
       </c>
-      <c r="G103" s="95" t="n">
+      <c r="G103" s="95">
         <v>1000</v>
       </c>
       <c r="H103" s="66" t="n"/>
@@ -3429,7 +3429,7 @@
           <t>20166;20167;20168;20169;20170;20171;20172</t>
         </is>
       </c>
-      <c r="G104" s="95" t="n">
+      <c r="G104" s="95">
         <v>1000</v>
       </c>
       <c r="H104" s="66" t="n"/>
@@ -3455,7 +3455,7 @@
           <t>20173;20174;20175;20176;20177;20178;20179</t>
         </is>
       </c>
-      <c r="G105" s="95" t="n">
+      <c r="G105" s="95">
         <v>1000</v>
       </c>
       <c r="H105" s="66" t="n"/>
@@ -3481,7 +3481,7 @@
           <t>20180;20181;20182;20183;20184;20185;20186</t>
         </is>
       </c>
-      <c r="G106" s="95" t="n">
+      <c r="G106" s="95">
         <v>1000</v>
       </c>
       <c r="H106" s="66" t="n"/>
@@ -3507,7 +3507,7 @@
           <t>20187;20188;20189;20190;20191;20192;20193</t>
         </is>
       </c>
-      <c r="G107" s="95" t="n">
+      <c r="G107" s="95">
         <v>1000</v>
       </c>
       <c r="H107" s="66" t="n"/>
@@ -3533,7 +3533,7 @@
           <t>20194;20195;20196;20197;20198;20199;20200</t>
         </is>
       </c>
-      <c r="G108" s="95" t="n">
+      <c r="G108" s="95">
         <v>1000</v>
       </c>
       <c r="H108" s="66" t="n"/>
@@ -3559,7 +3559,7 @@
           <t>20201;20202;20203;20204;20205;20206;20207</t>
         </is>
       </c>
-      <c r="G109" s="95" t="n">
+      <c r="G109" s="95">
         <v>1000</v>
       </c>
       <c r="H109" s="66" t="n">
@@ -3587,7 +3587,7 @@
           <t>20208;20209;20210;20211;20212;20213;20214</t>
         </is>
       </c>
-      <c r="G110" s="95" t="n">
+      <c r="G110" s="95">
         <v>1000</v>
       </c>
       <c r="H110" s="66" t="n"/>
@@ -3613,7 +3613,7 @@
           <t>20215;20216;20217;20218;20219;20220;20221</t>
         </is>
       </c>
-      <c r="G111" s="95" t="n">
+      <c r="G111" s="95">
         <v>1000</v>
       </c>
       <c r="H111" s="66" t="n"/>
@@ -3639,7 +3639,7 @@
           <t>20222;20223;20224;20225;20226;20227;20228</t>
         </is>
       </c>
-      <c r="G112" s="95" t="n">
+      <c r="G112" s="95">
         <v>1000</v>
       </c>
       <c r="H112" s="66" t="n"/>
@@ -3665,7 +3665,7 @@
           <t>20229;20230;20231;20232;20233;20234;20235</t>
         </is>
       </c>
-      <c r="G113" s="95" t="n">
+      <c r="G113" s="95">
         <v>1000</v>
       </c>
       <c r="H113" s="66" t="n"/>
@@ -3691,7 +3691,7 @@
           <t>20236;20237;20238;20239;20240;20241;20242</t>
         </is>
       </c>
-      <c r="G114" s="95" t="n">
+      <c r="G114" s="95">
         <v>1000</v>
       </c>
       <c r="H114" s="66" t="n"/>
@@ -3717,7 +3717,7 @@
           <t>20243;20244;20245;20246;20247;20248;20249</t>
         </is>
       </c>
-      <c r="G115" s="95" t="n">
+      <c r="G115" s="95">
         <v>1000</v>
       </c>
       <c r="H115" s="66" t="n"/>
@@ -3743,7 +3743,7 @@
           <t>20250;20251;20252;20253;20254;20255;20256</t>
         </is>
       </c>
-      <c r="G116" s="95" t="n">
+      <c r="G116" s="95">
         <v>1000</v>
       </c>
       <c r="H116" s="66" t="n"/>
@@ -3769,7 +3769,7 @@
           <t>20257;20258;20259;20260;20261;20262;20263</t>
         </is>
       </c>
-      <c r="G117" s="95" t="n">
+      <c r="G117" s="95">
         <v>1000</v>
       </c>
       <c r="H117" s="66" t="n"/>
@@ -3795,7 +3795,7 @@
           <t>20264;20265;20266;20267;20268;20269;20270</t>
         </is>
       </c>
-      <c r="G118" s="95" t="n">
+      <c r="G118" s="95">
         <v>1000</v>
       </c>
       <c r="H118" s="66" t="n"/>
@@ -3819,7 +3819,7 @@
           <t>20271</t>
         </is>
       </c>
-      <c r="G119" s="95" t="n">
+      <c r="G119" s="95">
         <v>1000</v>
       </c>
       <c r="H119" s="66" t="n"/>
@@ -3841,7 +3841,7 @@
           <t>20272</t>
         </is>
       </c>
-      <c r="G120" s="95" t="n">
+      <c r="G120" s="95">
         <v>1000</v>
       </c>
       <c r="H120" s="66" t="n"/>
@@ -3867,7 +3867,7 @@
           <t>20273;20274;20275;20276;20277;20278;20279</t>
         </is>
       </c>
-      <c r="G121" s="95" t="n">
+      <c r="G121" s="95">
         <v>1000</v>
       </c>
       <c r="H121" s="66" t="n"/>
@@ -3893,7 +3893,7 @@
           <t>20280;20281;20282;20283;20284;20285;20286</t>
         </is>
       </c>
-      <c r="G122" s="95" t="n">
+      <c r="G122" s="95">
         <v>1000</v>
       </c>
       <c r="H122" s="66" t="n"/>
@@ -3919,7 +3919,7 @@
           <t>20287;20288;20289;20290;20291;20292;20293</t>
         </is>
       </c>
-      <c r="G123" s="95" t="n">
+      <c r="G123" s="95">
         <v>1000</v>
       </c>
       <c r="H123" s="66" t="n"/>
@@ -3945,7 +3945,7 @@
           <t>20294;20295;20296;20297;20298;20299;20300</t>
         </is>
       </c>
-      <c r="G124" s="95" t="n">
+      <c r="G124" s="95">
         <v>1000</v>
       </c>
       <c r="H124" s="66" t="n"/>
@@ -3971,7 +3971,7 @@
           <t>20301;20302;20303;20304;20305;20306;20307</t>
         </is>
       </c>
-      <c r="G125" s="95" t="n">
+      <c r="G125" s="95">
         <v>1000</v>
       </c>
       <c r="H125" s="66" t="n"/>
@@ -3997,7 +3997,7 @@
           <t>20308;20309;20310;20311;20312;20313;20314</t>
         </is>
       </c>
-      <c r="G126" s="95" t="n">
+      <c r="G126" s="95">
         <v>1000</v>
       </c>
       <c r="H126" s="66" t="n"/>
@@ -4023,7 +4023,7 @@
           <t>20315;20316;20317;20318;20319;20320;20321</t>
         </is>
       </c>
-      <c r="G127" s="95" t="n">
+      <c r="G127" s="95">
         <v>1000</v>
       </c>
       <c r="H127" s="66" t="n"/>
@@ -4049,7 +4049,7 @@
           <t>20322;20323;20324;20325;20326;20327;20328</t>
         </is>
       </c>
-      <c r="G128" s="95" t="n">
+      <c r="G128" s="95">
         <v>1000</v>
       </c>
       <c r="H128" s="66" t="n"/>
@@ -4075,7 +4075,7 @@
           <t>20329;20330;20331;20332;20333;20334;20335</t>
         </is>
       </c>
-      <c r="G129" s="95" t="n">
+      <c r="G129" s="95">
         <v>1000</v>
       </c>
       <c r="H129" s="66" t="n"/>
@@ -4101,7 +4101,7 @@
           <t>20336;20337;20338;20339;20340;20341;20342</t>
         </is>
       </c>
-      <c r="G130" s="95" t="n">
+      <c r="G130" s="95">
         <v>1000</v>
       </c>
       <c r="H130" s="66" t="n"/>
@@ -4127,7 +4127,7 @@
           <t>20343;20344;20345;20346;20347;20348;20349</t>
         </is>
       </c>
-      <c r="G131" s="95" t="n">
+      <c r="G131" s="95">
         <v>1000</v>
       </c>
       <c r="H131" s="66" t="n"/>
@@ -4153,7 +4153,7 @@
           <t>20350;20351;20352;20353;20354;20355;20356</t>
         </is>
       </c>
-      <c r="G132" s="95" t="n">
+      <c r="G132" s="95">
         <v>1000</v>
       </c>
       <c r="H132" s="66" t="n"/>
@@ -4179,7 +4179,7 @@
           <t>20357;20358;20359;20360;20361;20362;20363</t>
         </is>
       </c>
-      <c r="G133" s="95" t="n">
+      <c r="G133" s="95">
         <v>1000</v>
       </c>
       <c r="H133" s="66" t="n"/>
@@ -4205,7 +4205,7 @@
           <t>20364;20365;20366;20367;20368;20369;20370</t>
         </is>
       </c>
-      <c r="G134" s="95" t="n">
+      <c r="G134" s="95">
         <v>1000</v>
       </c>
       <c r="H134" s="66" t="n"/>
@@ -4231,7 +4231,7 @@
           <t>20371;20372;20373;20374;20375;20376;20377</t>
         </is>
       </c>
-      <c r="G135" s="95" t="n">
+      <c r="G135" s="95">
         <v>1000</v>
       </c>
       <c r="H135" s="66" t="n"/>
@@ -4257,7 +4257,7 @@
           <t>20378;20379;20380;20381;20382;20383;20384</t>
         </is>
       </c>
-      <c r="G136" s="95" t="n">
+      <c r="G136" s="95">
         <v>1000</v>
       </c>
       <c r="H136" s="66" t="n"/>
@@ -4283,7 +4283,7 @@
           <t>20385;20386;20387;20388;20389;20390;20391</t>
         </is>
       </c>
-      <c r="G137" s="95" t="n">
+      <c r="G137" s="95">
         <v>1000</v>
       </c>
       <c r="H137" s="66" t="n"/>
@@ -4309,7 +4309,7 @@
           <t>20392;20393;20394;20395;20396;20397;20398</t>
         </is>
       </c>
-      <c r="G138" s="95" t="n">
+      <c r="G138" s="95">
         <v>1000</v>
       </c>
       <c r="H138" s="66" t="n"/>
@@ -4335,7 +4335,7 @@
           <t>20399;20400;20401;20402;20403;20404;20405</t>
         </is>
       </c>
-      <c r="G139" s="95" t="n">
+      <c r="G139" s="95">
         <v>1000</v>
       </c>
       <c r="H139" s="66" t="n"/>
@@ -4361,7 +4361,7 @@
           <t>20406;20407;20408;20409;20410;20411;20412</t>
         </is>
       </c>
-      <c r="G140" s="95" t="n">
+      <c r="G140" s="95">
         <v>1000</v>
       </c>
       <c r="H140" s="66" t="n"/>
@@ -4387,7 +4387,7 @@
           <t>20413;20414;20415;20416;20417;20418;20419</t>
         </is>
       </c>
-      <c r="G141" s="95" t="n">
+      <c r="G141" s="95">
         <v>1000</v>
       </c>
       <c r="H141" s="66" t="n"/>
@@ -4413,7 +4413,7 @@
           <t>20420;20421;20422;20423;20424;20425;20426</t>
         </is>
       </c>
-      <c r="G142" s="95" t="n">
+      <c r="G142" s="95">
         <v>1000</v>
       </c>
       <c r="H142" s="66" t="n"/>
@@ -4439,7 +4439,7 @@
           <t>20427;20428;20429;20430;20431;20432;20433</t>
         </is>
       </c>
-      <c r="G143" s="95" t="n">
+      <c r="G143" s="95">
         <v>1000</v>
       </c>
       <c r="H143" s="66" t="n"/>
@@ -4465,7 +4465,7 @@
           <t>20434;20435;20436;20437;20438;20439;20440</t>
         </is>
       </c>
-      <c r="G144" s="95" t="n">
+      <c r="G144" s="95">
         <v>1000</v>
       </c>
       <c r="H144" s="66" t="n"/>
@@ -4491,7 +4491,7 @@
           <t>20441;20442;20443;20444;20445;20446;20447</t>
         </is>
       </c>
-      <c r="G145" s="95" t="n">
+      <c r="G145" s="95">
         <v>1000</v>
       </c>
       <c r="H145" s="66" t="n"/>
@@ -4517,7 +4517,7 @@
           <t>20448;20449;20450;20451;20452;20453;20454</t>
         </is>
       </c>
-      <c r="G146" s="95" t="n">
+      <c r="G146" s="95">
         <v>1000</v>
       </c>
       <c r="H146" s="66" t="n"/>
@@ -4543,7 +4543,7 @@
           <t>20455;20456;20457;20458;20459;20460;20461</t>
         </is>
       </c>
-      <c r="G147" s="95" t="n">
+      <c r="G147" s="95">
         <v>1000</v>
       </c>
       <c r="H147" s="66" t="n"/>
@@ -4569,7 +4569,7 @@
           <t>20462;20463;20464;20465;20466;20467;20468</t>
         </is>
       </c>
-      <c r="G148" s="95" t="n">
+      <c r="G148" s="95">
         <v>1000</v>
       </c>
       <c r="H148" s="66" t="n"/>
@@ -4595,7 +4595,7 @@
           <t>20469;20470;20471;20472;20473;20474;20475</t>
         </is>
       </c>
-      <c r="G149" s="95" t="n">
+      <c r="G149" s="95">
         <v>1000</v>
       </c>
       <c r="H149" s="66" t="n"/>
@@ -4621,7 +4621,7 @@
           <t>20476;20477;20478;20479;20480;20481;20482</t>
         </is>
       </c>
-      <c r="G150" s="95" t="n">
+      <c r="G150" s="95">
         <v>1000</v>
       </c>
       <c r="H150" s="66" t="n"/>
@@ -4647,7 +4647,7 @@
           <t>20483;20484;20485;20486;20487;20488;20489</t>
         </is>
       </c>
-      <c r="G151" s="95" t="n">
+      <c r="G151" s="95">
         <v>1000</v>
       </c>
       <c r="H151" s="66" t="n"/>
@@ -4671,7 +4671,7 @@
           <t>20490</t>
         </is>
       </c>
-      <c r="G152" s="95" t="n">
+      <c r="G152" s="95">
         <v>1000</v>
       </c>
       <c r="H152" s="66" t="n"/>
@@ -4697,7 +4697,7 @@
           <t>20491;20492;20493;20494;20495;20496;20497</t>
         </is>
       </c>
-      <c r="G153" s="95" t="n">
+      <c r="G153" s="95">
         <v>1000</v>
       </c>
       <c r="H153" s="66" t="n"/>
@@ -4723,7 +4723,7 @@
           <t>20498;20499;20500;20501;20502;20503;20504</t>
         </is>
       </c>
-      <c r="G154" s="95" t="n">
+      <c r="G154" s="95">
         <v>1000</v>
       </c>
       <c r="H154" s="66" t="n"/>
@@ -4749,7 +4749,7 @@
           <t>20505;20506;20507;20508;20509;20510;20511</t>
         </is>
       </c>
-      <c r="G155" s="95" t="n">
+      <c r="G155" s="95">
         <v>1000</v>
       </c>
       <c r="H155" s="66" t="n"/>
@@ -4773,7 +4773,7 @@
           <t>20512</t>
         </is>
       </c>
-      <c r="G156" s="95" t="n">
+      <c r="G156" s="95">
         <v>1000</v>
       </c>
       <c r="H156" s="66" t="n"/>
